--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.78530134467184</v>
+        <v>9.227611468509174</v>
       </c>
       <c r="D2" t="n">
-        <v>56.6411826943871</v>
+        <v>9.204192187837904</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01095645004154</v>
+        <v>2.76428042313175</v>
       </c>
       <c r="F2" t="n">
-        <v>16.47392007198782</v>
+        <v>2.677012011698021</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.24833775365146</v>
+        <v>11.25285488496836</v>
       </c>
       <c r="D3" t="n">
-        <v>70.22284317279785</v>
+        <v>11.41121201557965</v>
       </c>
       <c r="E3" t="n">
-        <v>17.01095645004154</v>
+        <v>2.76428042313175</v>
       </c>
       <c r="F3" t="n">
-        <v>16.47392007198782</v>
+        <v>2.677012011698021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.38084494106997</v>
+        <v>8.02438730292387</v>
       </c>
       <c r="D4" t="n">
-        <v>49.78525730059749</v>
+        <v>8.090104311347092</v>
       </c>
       <c r="E4" t="n">
-        <v>17.01095645004154</v>
+        <v>2.76428042313175</v>
       </c>
       <c r="F4" t="n">
-        <v>16.47392007198782</v>
+        <v>2.677012011698021</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>90.26940210987246</v>
+        <v>14.66877784285428</v>
       </c>
       <c r="D5" t="n">
-        <v>89.29604612234864</v>
+        <v>14.51060749488165</v>
       </c>
       <c r="E5" t="n">
-        <v>17.01095645004154</v>
+        <v>2.76428042313175</v>
       </c>
       <c r="F5" t="n">
-        <v>16.47392007198782</v>
+        <v>2.677012011698021</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>91.09153855940841</v>
+        <v>14.80237501590387</v>
       </c>
       <c r="D6" t="n">
-        <v>90.12033266205077</v>
+        <v>14.64455405758325</v>
       </c>
       <c r="E6" t="n">
-        <v>17.01095645004154</v>
+        <v>2.76428042313175</v>
       </c>
       <c r="F6" t="n">
-        <v>16.47392007198782</v>
+        <v>2.677012011698021</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
